--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488243_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488243_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. BRAVO ORTEGA</t>
+          <t>J. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2449</v>
+        <v>4.0967</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3453</v>
+        <v>2.9289</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1004</v>
+        <v>1.1678</v>
       </c>
       <c r="G2" t="n">
-        <v>3.5242</v>
+        <v>1.0936</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2844</v>
+        <v>1.0521</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2398</v>
+        <v>0.0415</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2282</v>
+        <v>2.4178</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4817</v>
+        <v>1.6701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.7477</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.704</v>
+        <v>-1.3242</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1973</v>
+        <v>-0.618</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.5067</v>
+        <v>-0.7063</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9264</v>
+        <v>2.4087</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8529</v>
+        <v>2.4087</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6466</v>
+        <v>-0.3494</v>
       </c>
       <c r="T2" t="n">
-        <v>3.0082</v>
+        <v>-0.4327</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6384</v>
+        <v>0.0833</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0005</v>
+        <v>0.9439</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8883</v>
+        <v>0.9439</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.8877</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BRAVO ORTEGA</t>
+          <t>M. BRAVO ORTEGA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9193</v>
+        <v>3.7956</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1455</v>
+        <v>4.093</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7738</v>
+        <v>-0.2974</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0936</v>
+        <v>3.5242</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0521</v>
+        <v>3.2844</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0415</v>
+        <v>0.2398</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4178</v>
+        <v>4.2282</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6701</v>
+        <v>3.4817</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7477</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3242</v>
+        <v>-0.704</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.618</v>
+        <v>-0.1973</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7063</v>
+        <v>-0.5067</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4087</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4087</v>
+        <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5268</v>
+        <v>1.1972</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2162</v>
+        <v>0.7558</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3107</v>
+        <v>0.4414</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9439</v>
+        <v>0.0005</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9439</v>
+        <v>1.8883</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.8877</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Á. LLAMAS JIMENEZ</t>
+          <t>D. MORILLO LEON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6221</v>
+        <v>0.7796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6221</v>
+        <v>0.7118</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.0678</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6221</v>
+        <v>-0.1512</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0.1451</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6221</v>
+        <v>-0.0062</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6221</v>
+        <v>0.823</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.1074</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6221</v>
+        <v>0.7157</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.9743000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.2524</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.7219</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.0044</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.1113</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.1156</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MORILLO LEON</t>
+          <t>Á. LLAMAS JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.436</v>
+        <v>0.6221</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5159</v>
+        <v>0.6221</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0799</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1512</v>
+        <v>0.6221</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1451</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0062</v>
+        <v>0.6221</v>
       </c>
       <c r="J5" t="n">
-        <v>0.823</v>
+        <v>0.6221</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1074</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7157</v>
+        <v>0.6221</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9743000000000001</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2524</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7219</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3392</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3071</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0321</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2137</v>
+        <v>-0.0167</v>
       </c>
       <c r="E7" t="n">
         <v>-0.3887</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1751</v>
+        <v>0.372</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3487</v>
@@ -1000,13 +1000,13 @@
         <v>1.297</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2181</v>
+        <v>-0.0211</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0373</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1808</v>
+        <v>0.0161</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9439</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
+          <t>A. VEGUILLA SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.289</v>
+        <v>-0.2616</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8023</v>
+        <v>-0.9611</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5133</v>
+        <v>0.6995</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0433</v>
+        <v>-1.2254</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1735</v>
+        <v>0.9372</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2168</v>
+        <v>-2.1627</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9008</v>
+        <v>-1.3803</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1543</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7465000000000001</v>
+        <v>-1.9171</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8575</v>
+        <v>0.1549</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3278</v>
+        <v>0.4004</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.2456</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9264</v>
+        <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2977</v>
+        <v>-0.0917</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1467</v>
+        <v>0.1048</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4444</v>
+        <v>-0.1965</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7718</v>
+        <v>-0.5038</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5653</v>
+        <v>1.0549</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3371</v>
+        <v>-1.5587</v>
       </c>
       <c r="G9" t="n">
         <v>1.1616</v>
@@ -1156,13 +1156,13 @@
         <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2659</v>
+        <v>0.0022</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.235</v>
+        <v>0.2546</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0309</v>
+        <v>-0.2525</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VEGUILLA SANCHEZ</t>
+          <t>R. HENRIQUE RIBEIRO FORMOSO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1495</v>
+        <v>-0.7754</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7013</v>
+        <v>-0.8455</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5518</v>
+        <v>0.0701</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2254</v>
+        <v>0.0433</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9372</v>
+        <v>-0.1735</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.1627</v>
+        <v>0.2168</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3803</v>
+        <v>0.9008</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.1543</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.9171</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1549</v>
+        <v>-0.8575</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4004</v>
+        <v>-0.3278</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2456</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9797</v>
+        <v>-0.1887</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6354</v>
+        <v>-0.1899</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3442</v>
+        <v>0.0012</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0382</v>
+        <v>-1.9584</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4758</v>
+        <v>-1.519</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5625</v>
+        <v>-0.4394</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9171</v>
@@ -1312,13 +1312,13 @@
         <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6591</v>
+        <v>-0.5792</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.5729</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1294</v>
+        <v>-0.0062</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9444</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4824</v>
+        <v>-5.7232</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4036</v>
+        <v>-4.3489</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0788</v>
+        <v>-1.3743</v>
       </c>
       <c r="G12" t="n">
         <v>-2.2767</v>
@@ -1390,13 +1390,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0204</v>
+        <v>-0.2611</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6566</v>
+        <v>-0.6019</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6362</v>
+        <v>0.3407</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8883</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.2852</v>
+        <v>-5.789</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.2357</v>
+        <v>-3.8872</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0495</v>
+        <v>-1.9018</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0477</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5144</v>
+        <v>-1.0181</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9849</v>
+        <v>-0.6364</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5295</v>
+        <v>-0.3818</v>
       </c>
       <c r="V13" t="n">
         <v>0.315</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.6854</v>
+        <v>-5.412</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.491199999999998</v>
+        <v>-2.2176</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.1942</v>
+        <v>-3.1944</v>
       </c>
       <c r="G14" t="n">
         <v>-2.199899999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2506</v>
+        <v>4.250599999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-6.4506</v>
       </c>
       <c r="J14" t="n">
-        <v>6.260300000000001</v>
+        <v>6.260300000000003</v>
       </c>
       <c r="K14" t="n">
         <v>6.8763</v>
@@ -1528,13 +1528,13 @@
         <v>-0.6158999999999997</v>
       </c>
       <c r="M14" t="n">
-        <v>-8.460400000000002</v>
+        <v>-8.4604</v>
       </c>
       <c r="N14" t="n">
         <v>-2.6256</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.835099999999999</v>
+        <v>-5.8351</v>
       </c>
       <c r="P14" t="n">
         <v>0.9263000000000003</v>
@@ -1546,13 +1546,13 @@
         <v>12.97</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5793</v>
+        <v>-1.3055</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7407</v>
+        <v>-1.4672</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1614</v>
+        <v>0.1613000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8328</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.0417</v>
+        <v>5.863</v>
       </c>
       <c r="E15" t="n">
-        <v>5.4724</v>
+        <v>4.8848</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5693</v>
+        <v>0.9781</v>
       </c>
       <c r="G15" t="n">
         <v>2.6533</v>
@@ -1624,13 +1624,13 @@
         <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7601</v>
+        <v>0.5814</v>
       </c>
       <c r="T15" t="n">
-        <v>0.873</v>
+        <v>0.2854</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1129</v>
+        <v>0.2959</v>
       </c>
       <c r="V15" t="n">
         <v>1.8872</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5988</v>
+        <v>5.3354</v>
       </c>
       <c r="E16" t="n">
         <v>4.4889</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1098</v>
+        <v>0.8465</v>
       </c>
       <c r="G16" t="n">
         <v>3.574</v>
@@ -1702,13 +1702,13 @@
         <v>1.1117</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8951</v>
+        <v>0.6317</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2897</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1848</v>
+        <v>0.9214</v>
       </c>
       <c r="V16" t="n">
         <v>0.9444</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. HEPBURN</t>
+          <t>K. DELGADO YEBOAH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.4506</v>
+        <v>3.6782</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7039</v>
+        <v>3.4534</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7467</v>
+        <v>0.2248</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8442</v>
+        <v>-0.1507</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6229</v>
+        <v>-0.4114</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2213</v>
+        <v>0.2608</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0089</v>
+        <v>1.6701</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3714</v>
+        <v>0.8797</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3626</v>
+        <v>0.7905</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1647</v>
+        <v>-1.8208</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7485000000000001</v>
+        <v>-1.2911</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5839</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9264</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1117</v>
+        <v>-2.0382</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2532</v>
+        <v>0.2381</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1779</v>
+        <v>0.0454</v>
       </c>
       <c r="U17" t="n">
-        <v>1.0754</v>
+        <v>0.1927</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5733</v>
+        <v>3.776</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6289</v>
+        <v>3.776</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. DELGADO YEBOAH</t>
+          <t>P. HEPBURN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.337</v>
+        <v>3.6173</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8658</v>
+        <v>3.0184</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5288</v>
+        <v>0.599</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1507</v>
+        <v>3.8442</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4114</v>
+        <v>3.6229</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2608</v>
+        <v>0.2213</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6701</v>
+        <v>4.0089</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8797</v>
+        <v>4.3714</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7905</v>
+        <v>-0.3626</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8208</v>
+        <v>-0.1647</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2911</v>
+        <v>-0.7485000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5296999999999999</v>
+        <v>0.5839</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1853</v>
+        <v>0.9264</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0382</v>
+        <v>-1.1117</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.103</v>
+        <v>0.42</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5422</v>
+        <v>-0.5077</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5609</v>
+        <v>0.9277</v>
       </c>
       <c r="V18" t="n">
-        <v>3.776</v>
+        <v>-1.5733</v>
       </c>
       <c r="W18" t="n">
-        <v>3.776</v>
+        <v>0.6289</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0872</v>
+        <v>-0.1967</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.415</v>
+        <v>-1.8274</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3278</v>
+        <v>1.6307</v>
       </c>
       <c r="G20" t="n">
         <v>1.9128</v>
@@ -2014,13 +2014,13 @@
         <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2033</v>
+        <v>-0.3128</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8754</v>
+        <v>-0.2879</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3278</v>
+        <v>-0.0249</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.271</v>
+        <v>-1.5689</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0868</v>
+        <v>0.4786</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3579</v>
+        <v>-2.0475</v>
       </c>
       <c r="G21" t="n">
         <v>0.0289</v>
@@ -2092,13 +2092,13 @@
         <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4683</v>
+        <v>0.2338</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0709</v>
+        <v>0.3209</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3975</v>
+        <v>-0.0871</v>
       </c>
       <c r="V21" t="n">
         <v>-2.2022</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3573</v>
+        <v>-4.6511</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4286</v>
+        <v>-5.7224</v>
       </c>
       <c r="F22" t="n">
         <v>1.0713</v>
@@ -2170,10 +2170,10 @@
         <v>1.1117</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.2621</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3457</v>
+        <v>0.0519</v>
       </c>
       <c r="U22" t="n">
         <v>0.2101</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.349</v>
+        <v>-5.408</v>
       </c>
       <c r="E23" t="n">
         <v>-5.9021</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5531</v>
+        <v>0.4942</v>
       </c>
       <c r="G23" t="n">
         <v>-5.6828</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8895999999999999</v>
+        <v>0.8307</v>
       </c>
       <c r="T23" t="n">
         <v>0.2201</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6695</v>
+        <v>0.6105</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.685700000000001</v>
+        <v>6.9913</v>
       </c>
       <c r="E24" t="n">
-        <v>3.194200000000003</v>
+        <v>3.194299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4913</v>
+        <v>3.7971</v>
       </c>
       <c r="G24" t="n">
         <v>2.200099999999999</v>
@@ -2326,13 +2326,13 @@
         <v>12.0437</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5793</v>
+        <v>2.885</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1615000000000001</v>
+        <v>-0.1616</v>
       </c>
       <c r="U24" t="n">
-        <v>1.7407</v>
+        <v>3.0463</v>
       </c>
       <c r="V24" t="n">
         <v>2.8327</v>
